--- a/data/trans_dic/P34B03_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P34B03_R-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación, 3 veces por semana o más</t>
+          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic, correr, natación, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 17,08</t>
+          <t>11,9; 17,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,41; 17,65</t>
+          <t>12,38; 18,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,54; 17,74</t>
+          <t>10,53; 17,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,74</t>
+          <t>3,52; 6,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,43</t>
+          <t>5,51; 9,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,68</t>
+          <t>5,03; 8,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,26</t>
+          <t>8,02; 11,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 12,75</t>
+          <t>9,52; 12,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,27; 12,02</t>
+          <t>8,18; 12,12</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,67; 16,02</t>
+          <t>11,76; 16,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,54; 19,36</t>
+          <t>14,63; 19,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 22,03</t>
+          <t>7,79; 21,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,36</t>
+          <t>5,23; 8,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,5</t>
+          <t>7,89; 11,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,67</t>
+          <t>7,01; 10,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,92; 11,71</t>
+          <t>8,99; 11,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 14,82</t>
+          <t>11,76; 14,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 15,35</t>
+          <t>8,16; 15,52</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,4; 21,47</t>
+          <t>15,48; 21,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,5; 18,57</t>
+          <t>13,34; 18,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,07; 18,98</t>
+          <t>12,01; 19,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,9</t>
+          <t>4,98; 8,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 11,46</t>
+          <t>7,26; 11,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,21</t>
+          <t>2,91; 8,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 14,3</t>
+          <t>10,85; 14,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,88; 14,3</t>
+          <t>10,84; 14,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 12,57</t>
+          <t>6,71; 12,56</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 18,86</t>
+          <t>14,1; 19,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 21,21</t>
+          <t>16,67; 21,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,76; 22,75</t>
+          <t>16,53; 22,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 9,03</t>
+          <t>5,9; 9,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,14</t>
+          <t>9,34; 13,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,42</t>
+          <t>7,53; 11,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 13,13</t>
+          <t>10,34; 13,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,08; 16,32</t>
+          <t>13,26; 16,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,17; 15,98</t>
+          <t>11,87; 15,96</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,35; 16,95</t>
+          <t>14,27; 16,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,63; 18,2</t>
+          <t>15,51; 18,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,25; 18,7</t>
+          <t>12,87; 18,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,56</t>
+          <t>5,77; 7,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,45; 10,5</t>
+          <t>8,51; 10,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,03</t>
+          <t>6,4; 8,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,26; 11,78</t>
+          <t>10,21; 11,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,31; 13,96</t>
+          <t>12,27; 13,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,27</t>
+          <t>10,5; 13,31</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación, 3 veces por semana o más</t>
+          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic, correr, natación, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80884; 119934</t>
+          <t>83550; 121148</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83709; 119133</t>
+          <t>83555; 121483</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66862; 112530</t>
+          <t>66818; 113389</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23441; 46989</t>
+          <t>24513; 47381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36825; 63418</t>
+          <t>37097; 62790</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34543; 58494</t>
+          <t>33896; 57003</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>111739; 157547</t>
+          <t>112200; 157805</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>127421; 171799</t>
+          <t>128254; 172666</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>108257; 157267</t>
+          <t>106990; 158562</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>118797; 163067</t>
+          <t>119662; 165393</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>148633; 197980</t>
+          <t>149588; 198773</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>106395; 262573</t>
+          <t>92900; 260850</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53395; 86121</t>
+          <t>53847; 86926</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81937; 119972</t>
+          <t>82323; 121506</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67066; 102228</t>
+          <t>67140; 102095</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>182768; 239757</t>
+          <t>184186; 238309</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>242523; 305997</t>
+          <t>242877; 305214</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>185524; 330101</t>
+          <t>175443; 333621</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>116638; 162692</t>
+          <t>117276; 160675</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>102566; 141085</t>
+          <t>101359; 142720</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85056; 133761</t>
+          <t>84607; 133871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39099; 69157</t>
+          <t>38741; 66762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>57080; 89955</t>
+          <t>56995; 87983</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31966; 85998</t>
+          <t>27127; 82804</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>165521; 219527</t>
+          <t>166579; 223737</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>168047; 220862</t>
+          <t>167381; 218271</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>106414; 205932</t>
+          <t>109993; 205669</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>132800; 178542</t>
+          <t>133499; 180164</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>150809; 198835</t>
+          <t>156251; 204274</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>155292; 210810</t>
+          <t>153174; 209090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62517; 94976</t>
+          <t>62086; 96343</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>95410; 137170</t>
+          <t>97499; 138153</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81545; 124601</t>
+          <t>82138; 123759</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>203009; 262398</t>
+          <t>206667; 263795</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>259235; 323343</t>
+          <t>262778; 327800</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>245558; 322320</t>
+          <t>239430; 322106</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>491617; 580500</t>
+          <t>488666; 574007</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>530515; 617833</t>
+          <t>526414; 614737</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458096; 646747</t>
+          <t>445002; 644667</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>204231; 268913</t>
+          <t>205139; 265688</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>299589; 372128</t>
+          <t>301638; 373426</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>231399; 330164</t>
+          <t>234173; 327856</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>716225; 822701</t>
+          <t>712616; 823438</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>854371; 968685</t>
+          <t>851221; 963781</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>747120; 943736</t>
+          <t>746871; 946601</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B03_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P34B03_R-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,9; 17,25</t>
+          <t>11,65; 17,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,38; 18,0</t>
+          <t>12,35; 17,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,53; 17,87</t>
+          <t>9,94; 16,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,8</t>
+          <t>3,27; 6,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,33</t>
+          <t>5,44; 9,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,46</t>
+          <t>5,23; 8,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,28</t>
+          <t>8,09; 11,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 12,81</t>
+          <t>9,47; 13,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,12</t>
+          <t>8,2; 11,87</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 16,25</t>
+          <t>11,65; 16,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 19,44</t>
+          <t>14,62; 19,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 21,88</t>
+          <t>17,17; 23,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,44</t>
+          <t>5,14; 8,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 11,65</t>
+          <t>7,82; 11,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,66</t>
+          <t>6,99; 10,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 11,63</t>
+          <t>8,92; 11,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 14,78</t>
+          <t>11,79; 14,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,16; 15,52</t>
+          <t>12,6; 16,33</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,48; 21,21</t>
+          <t>15,37; 21,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,34; 18,79</t>
+          <t>13,25; 18,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,01; 19,0</t>
+          <t>11,98; 18,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,59</t>
+          <t>4,86; 8,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 11,21</t>
+          <t>7,32; 11,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,87</t>
+          <t>6,51; 10,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 14,58</t>
+          <t>10,82; 14,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 14,13</t>
+          <t>10,87; 14,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,56</t>
+          <t>9,94; 13,65</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 19,03</t>
+          <t>13,82; 18,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,67; 21,79</t>
+          <t>16,68; 21,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,53; 22,56</t>
+          <t>17,17; 23,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,16</t>
+          <t>5,94; 9,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,24</t>
+          <t>9,2; 13,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,34</t>
+          <t>8,52; 12,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,34; 13,2</t>
+          <t>10,23; 13,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,26; 16,54</t>
+          <t>13,3; 16,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 15,96</t>
+          <t>13,3; 16,67</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,27; 16,76</t>
+          <t>14,36; 16,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,51; 18,11</t>
+          <t>15,55; 18,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,87; 18,64</t>
+          <t>15,85; 19,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,47</t>
+          <t>5,74; 7,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,54</t>
+          <t>8,56; 10,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,97</t>
+          <t>7,82; 9,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,21; 11,8</t>
+          <t>10,22; 11,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,27; 13,89</t>
+          <t>12,21; 13,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,31</t>
+          <t>12,06; 13,81</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86041</t>
+          <t>89561</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44806</t>
+          <t>49535</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>130847</t>
+          <t>139097</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>83550; 121148</t>
+          <t>81836; 120618</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83555; 121483</t>
+          <t>83370; 120223</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66818; 113389</t>
+          <t>68562; 113399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24513; 47381</t>
+          <t>22783; 45582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37097; 62790</t>
+          <t>36629; 63234</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33896; 57003</t>
+          <t>38239; 65179</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>112200; 157805</t>
+          <t>113201; 159173</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>128254; 172666</t>
+          <t>127581; 175698</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>106990; 158562</t>
+          <t>116543; 168665</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195753</t>
+          <t>210744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82738</t>
+          <t>91560</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>278491</t>
+          <t>302304</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>119662; 165393</t>
+          <t>118604; 163852</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>149588; 198773</t>
+          <t>149479; 198520</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92900; 260850</t>
+          <t>179903; 248974</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53847; 86926</t>
+          <t>52979; 86671</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82323; 121506</t>
+          <t>81541; 121929</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67140; 102095</t>
+          <t>74881; 113411</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>184186; 238309</t>
+          <t>182785; 240010</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>242877; 305214</t>
+          <t>243439; 307831</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>175443; 333621</t>
+          <t>266875; 345890</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107670</t>
+          <t>119472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58734</t>
+          <t>67541</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166404</t>
+          <t>187013</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>117276; 160675</t>
+          <t>116447; 162593</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>101359; 142720</t>
+          <t>100671; 143418</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84607; 133871</t>
+          <t>96232; 146182</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38741; 66762</t>
+          <t>37802; 67473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56995; 87983</t>
+          <t>57434; 89461</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27127; 82804</t>
+          <t>52872; 85566</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>166579; 223737</t>
+          <t>166057; 217832</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>167381; 218271</t>
+          <t>167939; 224563</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>109993; 205669</t>
+          <t>160505; 220433</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181837</t>
+          <t>198145</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>102905</t>
+          <t>113745</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>284742</t>
+          <t>311891</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>133499; 180164</t>
+          <t>130889; 176886</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>156251; 204274</t>
+          <t>156415; 202974</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>153174; 209090</t>
+          <t>169770; 227498</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62086; 96343</t>
+          <t>62473; 98153</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>97499; 138153</t>
+          <t>96052; 137397</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82138; 123759</t>
+          <t>95068; 136566</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>206667; 263795</t>
+          <t>204512; 263529</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>262778; 327800</t>
+          <t>263473; 326205</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>239430; 322106</t>
+          <t>279984; 350956</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>571302</t>
+          <t>617923</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>289183</t>
+          <t>322382</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>860485</t>
+          <t>940305</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>488666; 574007</t>
+          <t>491824; 580729</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>526414; 614737</t>
+          <t>527845; 612864</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>445002; 644667</t>
+          <t>559498; 671450</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>205139; 265688</t>
+          <t>204238; 268317</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>301638; 373426</t>
+          <t>303350; 371998</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>234173; 327856</t>
+          <t>291739; 358017</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>712616; 823438</t>
+          <t>713439; 818433</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>851221; 963781</t>
+          <t>847413; 967557</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>746871; 946601</t>
+          <t>875777; 1002298</t>
         </is>
       </c>
     </row>
